--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AE5168-3EC7-4A24-AFDB-D0E99194E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE59CCA-ECA9-4AE8-85E6-DA9B642F2A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
+    <t>S3aH2,S2aH2,S1aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S3aH1,S2aH3,S1aH1,S4aH3,S2aH1,S3aH3,S4aH1</t>
+    <t>S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S2aH1,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S3aH1,S2aH3,S1aH1,S4aH3,S2aH1,S3aH3,S4aH1</v>
+        <v>S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S2aH1,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
+        <v>S3aH2,S2aH2,S1aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE6C104-93C7-41E9-89EC-F499E8D0C52B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E0A346-1737-412F-B8E4-023CA0E5B0AF}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23548189-9C9E-49E0-92F5-1238062C6268}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B209B5-D86D-45F8-85A2-E1661771ED16}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6096CF8E-AEAC-48A1-A815-FF2659710972}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45855C2A-6850-4012-B269-B330C311DD92}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C31490E-B63D-4B7D-9537-6F0A9E662CC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE14AF4-894A-4069-B23E-881D2DBB2C77}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43658,7 +43658,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>315</v>
@@ -43966,7 +43966,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>315</v>
@@ -44167,7 +44167,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>315</v>
@@ -44466,7 +44466,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>315</v>
@@ -44522,7 +44522,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>315</v>
@@ -44578,7 +44578,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>315</v>
@@ -44592,7 +44592,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>315</v>
@@ -44634,7 +44634,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="S50" t="s">
         <v>315</v>
@@ -44648,7 +44648,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>315</v>
@@ -44662,7 +44662,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>315</v>
@@ -44690,7 +44690,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="S54" t="s">
         <v>315</v>
@@ -44732,7 +44732,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="S57" t="s">
         <v>315</v>
@@ -44760,7 +44760,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>315</v>
@@ -44788,7 +44788,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>315</v>
@@ -44830,7 +44830,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>315</v>
@@ -44844,7 +44844,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="S65" t="s">
         <v>315</v>
@@ -44858,7 +44858,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>315</v>
@@ -44872,7 +44872,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>315</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>315</v>
@@ -44956,7 +44956,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>315</v>
@@ -45012,7 +45012,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>315</v>
@@ -45222,7 +45222,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>315</v>
@@ -45250,7 +45250,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="S94" t="s">
         <v>315</v>
@@ -45376,7 +45376,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>315</v>
@@ -45418,7 +45418,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>315</v>
@@ -45432,7 +45432,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>315</v>
@@ -45446,7 +45446,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>315</v>
@@ -45600,7 +45600,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>315</v>
@@ -45656,7 +45656,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>315</v>
@@ -45670,7 +45670,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>315</v>
@@ -45684,7 +45684,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>315</v>
@@ -45698,7 +45698,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>315</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE59CCA-ECA9-4AE8-85E6-DA9B642F2A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50288A1-08BD-4480-9568-42FDDBDC286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S2aH2,S1aH2,S4aH2</t>
+    <t>S2aH2,S4aH2,S1aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S2aH1,S2aH3</t>
+    <t>S3aH3,S4aH1,S3aH1,S2aH1,S2aH3,S1aH3,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S2aH1,S2aH3</v>
+        <v>S3aH3,S4aH1,S3aH1,S2aH1,S2aH3,S1aH3,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S2aH2,S1aH2,S4aH2</v>
+        <v>S2aH2,S4aH2,S1aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E0A346-1737-412F-B8E4-023CA0E5B0AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3A1237-87E3-4495-B755-A6BBCA8E09D7}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B209B5-D86D-45F8-85A2-E1661771ED16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DC3118-50A3-4631-B3C0-3500E0D5497D}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45855C2A-6850-4012-B269-B330C311DD92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E13D5C-0E0B-4C3C-ADD0-1FCE38DEC571}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE14AF4-894A-4069-B23E-881D2DBB2C77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD3DC27-76B6-48C7-A97B-F479EAB6CC2D}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43658,7 +43658,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>315</v>
@@ -44010,7 +44010,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>315</v>
@@ -44420,7 +44420,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>315</v>
@@ -44550,7 +44550,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>315</v>
@@ -44662,7 +44662,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>315</v>
@@ -44718,7 +44718,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>315</v>
@@ -44886,7 +44886,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>315</v>
@@ -45110,7 +45110,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>315</v>
@@ -45222,7 +45222,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>315</v>
@@ -45390,7 +45390,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>315</v>
@@ -45446,7 +45446,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>315</v>
@@ -45558,7 +45558,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>315</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50288A1-08BD-4480-9568-42FDDBDC286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE64B741-5069-474C-A377-964981EA1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S1aH2,S3aH2</t>
+    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S3aH1,S2aH1,S2aH3,S1aH3,S1aH1,S4aH3</t>
+    <t>S3aH3,S4aH1,S1aH3,S3aH1,S2aH3,S2aH1,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S3aH1,S2aH1,S2aH3,S1aH3,S1aH1,S4aH3</v>
+        <v>S3aH3,S4aH1,S1aH3,S3aH1,S2aH3,S2aH1,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S1aH2,S3aH2</v>
+        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3A1237-87E3-4495-B755-A6BBCA8E09D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D75BC557-2564-4E20-B6D8-46A751DEC890}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DC3118-50A3-4631-B3C0-3500E0D5497D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E368A78-EB2B-41A6-94A9-C758FA9BC78E}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E13D5C-0E0B-4C3C-ADD0-1FCE38DEC571}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1453DEB8-F533-416C-A0F8-25392F01B659}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD3DC27-76B6-48C7-A97B-F479EAB6CC2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6DBFD4-B560-4998-9109-40563795E74B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44010,7 +44010,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>315</v>
@@ -44420,7 +44420,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>315</v>
@@ -44550,7 +44550,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>315</v>
@@ -44718,7 +44718,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>315</v>
@@ -44830,7 +44830,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>315</v>
@@ -44886,7 +44886,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>315</v>
@@ -45110,7 +45110,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>315</v>
@@ -45390,7 +45390,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>315</v>
@@ -45558,7 +45558,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>315</v>
@@ -45670,7 +45670,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>315</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE64B741-5069-474C-A377-964981EA1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CA1B28-8DA9-4C70-91FE-51BC6FCAAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
+    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S1aH3,S3aH1,S2aH3,S2aH1,S1aH1,S4aH3</t>
+    <t>S2aH3,S1aH1,S4aH3,S3aH1,S1aH3,S3aH3,S4aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S1aH3,S3aH1,S2aH3,S2aH1,S1aH1,S4aH3</v>
+        <v>S2aH3,S1aH1,S4aH3,S3aH1,S1aH3,S3aH3,S4aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
+        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D75BC557-2564-4E20-B6D8-46A751DEC890}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29AAB019-7B06-435A-956F-FCECA4331153}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E368A78-EB2B-41A6-94A9-C758FA9BC78E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68140779-1505-42D2-890D-E93B4557D4D3}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1453DEB8-F533-416C-A0F8-25392F01B659}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF2E32B-A80C-4C55-9536-4F36AFC7A41A}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6DBFD4-B560-4998-9109-40563795E74B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B80B077-C965-4530-A1C5-43127BC1E076}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44010,7 +44010,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>315</v>
@@ -44054,7 +44054,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>315</v>
@@ -44420,7 +44420,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>315</v>
@@ -44550,7 +44550,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>315</v>
@@ -44718,7 +44718,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>315</v>
@@ -44788,7 +44788,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>315</v>
@@ -44830,7 +44830,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>315</v>
@@ -44886,7 +44886,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>315</v>
@@ -44956,7 +44956,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>315</v>
@@ -45012,7 +45012,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>315</v>
@@ -45110,7 +45110,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>315</v>
@@ -45390,7 +45390,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>315</v>
@@ -45404,7 +45404,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>315</v>
@@ -45558,7 +45558,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>315</v>
@@ -45670,7 +45670,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>315</v>
@@ -45684,7 +45684,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>315</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CA1B28-8DA9-4C70-91FE-51BC6FCAAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46D871C-08F0-442A-BBA9-565FA8F8CBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
+    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S1aH1,S4aH3,S3aH1,S1aH3,S3aH3,S4aH1,S2aH1</t>
+    <t>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S1aH1,S4aH3,S3aH1,S1aH3,S3aH3,S4aH1,S2aH1</v>
+        <v>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
+        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29AAB019-7B06-435A-956F-FCECA4331153}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360C0088-8451-49AB-81E0-21D02E22EAEC}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68140779-1505-42D2-890D-E93B4557D4D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E8B430-1C8A-4E1A-B154-7ADA1AB6E6EB}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF2E32B-A80C-4C55-9536-4F36AFC7A41A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76924950-9111-4EBA-BF20-C3D2A3DC8A18}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B80B077-C965-4530-A1C5-43127BC1E076}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF371C87-902F-42FE-AF94-D26D850372DB}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43658,7 +43658,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>315</v>
@@ -43746,7 +43746,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>315</v>
@@ -43790,7 +43790,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>315</v>
@@ -44010,7 +44010,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>315</v>
@@ -44054,7 +44054,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="S21" t="s">
         <v>315</v>
@@ -44420,7 +44420,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>315</v>
@@ -44466,7 +44466,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>315</v>
@@ -44522,7 +44522,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>315</v>
@@ -44550,7 +44550,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>315</v>
@@ -44578,7 +44578,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>315</v>
@@ -44592,7 +44592,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>315</v>
@@ -44662,7 +44662,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>315</v>
@@ -44718,7 +44718,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>315</v>
@@ -44760,7 +44760,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>315</v>
@@ -44788,7 +44788,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>315</v>
@@ -44858,7 +44858,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>315</v>
@@ -44872,7 +44872,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>315</v>
@@ -44886,7 +44886,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>315</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>315</v>
@@ -44956,7 +44956,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>315</v>
@@ -45012,7 +45012,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>315</v>
@@ -45040,7 +45040,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>315</v>
@@ -45096,7 +45096,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>315</v>
@@ -45110,7 +45110,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>315</v>
@@ -45208,7 +45208,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>315</v>
@@ -45222,7 +45222,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>315</v>
@@ -45390,7 +45390,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>315</v>
@@ -45404,7 +45404,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>315</v>
@@ -45418,7 +45418,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>315</v>
@@ -45446,7 +45446,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>315</v>
@@ -45488,7 +45488,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>315</v>
@@ -45558,7 +45558,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>315</v>
@@ -45600,7 +45600,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>315</v>
@@ -45642,7 +45642,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="S122" t="s">
         <v>315</v>
@@ -45684,7 +45684,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>315</v>
@@ -45698,7 +45698,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>315</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46D871C-08F0-442A-BBA9-565FA8F8CBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21ADA3F-08CA-42AA-A245-789438A3EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,13 +954,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
+    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
+    <t>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S2aH1,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
+        <v>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S2aH1,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
+        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1688,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360C0088-8451-49AB-81E0-21D02E22EAEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB09AEFF-3054-4E22-A3D6-326A760A0D16}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1768,7 +1768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E8B430-1C8A-4E1A-B154-7ADA1AB6E6EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D806FF76-1C2E-4BB0-A9AA-7C7F11296CE5}">
   <dimension ref="B9:O622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18894,7 +18894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76924950-9111-4EBA-BF20-C3D2A3DC8A18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44EAADD4-1F91-4B00-880A-081950E89FA4}">
   <dimension ref="B9:CI120"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43507,7 +43507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF371C87-902F-42FE-AF94-D26D850372DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E92A9558-5E82-4548-80B7-417FF6004774}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43658,7 +43658,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>315</v>
@@ -43746,7 +43746,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>315</v>
@@ -44054,7 +44054,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>315</v>
@@ -44466,7 +44466,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>315</v>
@@ -44522,7 +44522,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>315</v>
@@ -44578,7 +44578,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>315</v>
@@ -44662,7 +44662,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>315</v>
@@ -44788,7 +44788,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>315</v>
@@ -44830,7 +44830,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>315</v>
@@ -44858,7 +44858,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>315</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>315</v>
@@ -44956,7 +44956,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>315</v>
@@ -45012,7 +45012,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>315</v>
@@ -45222,7 +45222,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>315</v>
@@ -45404,7 +45404,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>315</v>
@@ -45418,7 +45418,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>315</v>
@@ -45446,7 +45446,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>315</v>
@@ -45642,7 +45642,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>315</v>
@@ -45670,7 +45670,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>315</v>
@@ -45684,7 +45684,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>315</v>
@@ -45698,7 +45698,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>315</v>
